--- a/resources/formatos/FormatoPiezometroCasagrande.xlsx
+++ b/resources/formatos/FormatoPiezometroCasagrande.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\E-Monitoring-SqlServer\resources\formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\E-Monitoring-SqlServer\resources\formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80227F7A-7FC9-4AA9-ADCF-C40909E96D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124C494B-EC53-4B8F-9451-444672D93A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Piezometro" sheetId="1" r:id="rId1"/>
@@ -33,21 +33,9 @@
     <t>Nombre:</t>
   </si>
   <si>
-    <t>Cota Fondo Pozo (m.s.n.m):</t>
-  </si>
-  <si>
-    <t>Inclinación:</t>
-  </si>
-  <si>
     <t>Código:</t>
   </si>
   <si>
-    <t>Cota Fundación (m.s.n.m):</t>
-  </si>
-  <si>
-    <t>Azimuth:</t>
-  </si>
-  <si>
     <t>Stick Up (m):</t>
   </si>
   <si>
@@ -78,9 +66,6 @@
     <t>Coordenada Norte (m):</t>
   </si>
   <si>
-    <t>Cota de Superficie Actual (m.s.n.m):</t>
-  </si>
-  <si>
     <t>Piezometro1</t>
   </si>
   <si>
@@ -91,6 +76,21 @@
   </si>
   <si>
     <t>* El formato de hora: hh:mm:ss</t>
+  </si>
+  <si>
+    <t>Inclinación (°):</t>
+  </si>
+  <si>
+    <t>Azimuth (°):</t>
+  </si>
+  <si>
+    <t>Cota Fondo Pozo (msnm):</t>
+  </si>
+  <si>
+    <t>Cota Fundación (msnm):</t>
+  </si>
+  <si>
+    <t>Cota de Superficie Actual (msnm):</t>
   </si>
 </sst>
 </file>
@@ -435,27 +435,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -471,58 +510,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -870,215 +870,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31"/>
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19"/>
+      <c r="B1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+    </row>
+    <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="31"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="26"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="23"/>
+      <c r="C11" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="18"/>
-    </row>
-    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="21"/>
-    </row>
-    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21"/>
-    </row>
-    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="24"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="D11" s="26"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="26">
+        <v>0</v>
+      </c>
+      <c r="D12" s="26"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="B13" s="23"/>
+      <c r="C13" s="26">
+        <v>0</v>
+      </c>
+      <c r="D13" s="26"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="26">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="26">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="27"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="B16" s="23"/>
+      <c r="C16" s="26">
         <v>0</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="13" t="s">
+      <c r="D16" s="26"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="26">
+        <v>90</v>
+      </c>
+      <c r="D17" s="26"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="B18" s="23"/>
+      <c r="C18" s="26">
+        <v>0</v>
+      </c>
+      <c r="D18" s="26"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="26">
+        <v>0</v>
+      </c>
+      <c r="D19" s="26"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="13">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="13">
-        <v>90</v>
-      </c>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>44166</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>44180</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1086,11 +1086,13 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C10:D10"/>
@@ -1107,13 +1109,11 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="B1:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A1:A4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
